--- a/risorse/Risorsa_10_CRM_Minimo.xlsx
+++ b/risorse/Risorsa_10_CRM_Minimo.xlsx
@@ -17,11 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="€ #,##0;[Red]-€ #,##0;-"/>
-    <numFmt numFmtId="165" formatCode="0&quot;%&quot;"/>
-  </numFmts>
-  <fonts count="6">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,33 +27,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <color rgb="001E3A5F"/>
+      <sz val="15"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="0000838F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
+      <color rgb="00555555"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E3A5F"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -65,21 +55,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000BCD4"/>
+        <fgColor rgb="001E3A5F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000A1F2E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0000838F"/>
+        <fgColor rgb="00E8F4FD"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -87,87 +72,23 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CFD8DC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CFD8DC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CFD8DC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CFD8DC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C8E6C9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFCDD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFE0B2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00BBDEFB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -532,34 +453,34 @@
   <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AIOsha · Risorsa 10 — CRM Minimo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>AI Osha — Risorsa 10 · CRM Minimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sostituisce 6 fogli sparsi con un solo file</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
+          <t>Un solo file al posto di sei fogli sparsi. Il valore pesato e la Pipeline si calcolano da soli.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>ID</t>
@@ -617,53 +538,48 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Mario Rossi</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Rossi SRL</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>mario@rossi.it</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>+39 333 1234567</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Qualificato</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" t="n">
         <v>5000</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" t="n">
         <v>60</v>
       </c>
-      <c r="J5" s="5">
-        <f>H5*I5/100</f>
-        <v/>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>Da definire</t>
-        </is>
+      <c r="J5">
+        <f>IF(H5="","",H5*I5/100)</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -700,70 +616,61 @@
           <t>Proposta inviata</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="4" t="n">
         <v>12000</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="J6" s="5">
-        <f>H6*I6/100</f>
-        <v/>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>Da definire</t>
-        </is>
-      </c>
+      <c r="J6" s="4">
+        <f>IF(H6="","",H6*I6/100)</f>
+        <v/>
+      </c>
+      <c r="K6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Luca Verdi</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Verdi Spa</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>luca.verdi@verdispa.com</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>+39 348 1112233</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Sito web</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Primo contatto</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" t="n">
         <v>3500</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" t="n">
         <v>30</v>
       </c>
-      <c r="J7" s="5">
-        <f>H7*I7/100</f>
-        <v/>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>Da definire</t>
-        </is>
+      <c r="J7">
+        <f>IF(H7="","",H7*I7/100)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -800,70 +707,61 @@
           <t>Negoziazione</t>
         </is>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="4" t="n">
         <v>8000</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="J8" s="5">
-        <f>H8*I8/100</f>
-        <v/>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>Da definire</t>
-        </is>
-      </c>
+      <c r="J8" s="4">
+        <f>IF(H8="","",H8*I8/100)</f>
+        <v/>
+      </c>
+      <c r="K8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Paolo Gialli</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Gialli SRL</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>info@gialli.it</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>+39 320 9988776</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Newsletter</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Vinto</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" t="n">
         <v>6500</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" t="n">
         <v>100</v>
       </c>
-      <c r="J9" s="5">
-        <f>H9*I9/100</f>
-        <v/>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>Da definire</t>
-        </is>
+      <c r="J9">
+        <f>IF(H9="","",H9*I9/100)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -876,31 +774,22 @@
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="5">
-        <f>IF(AND(ISNUMBER(H10),ISNUMBER(I10)),H10*I10/100,"")</f>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4">
+        <f>IF(H10="","",H10*I10/100)</f>
         <v/>
       </c>
       <c r="K10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="5">
-        <f>IF(AND(ISNUMBER(H11),ISNUMBER(I11)),H11*I11/100,"")</f>
-        <v/>
-      </c>
-      <c r="K11" s="4" t="n"/>
+      <c r="J11">
+        <f>IF(H11="","",H11*I11/100)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -912,31 +801,22 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="5">
-        <f>IF(AND(ISNUMBER(H12),ISNUMBER(I12)),H12*I12/100,"")</f>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4">
+        <f>IF(H12="","",H12*I12/100)</f>
         <v/>
       </c>
       <c r="K12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="5">
-        <f>IF(AND(ISNUMBER(H13),ISNUMBER(I13)),H13*I13/100,"")</f>
-        <v/>
-      </c>
-      <c r="K13" s="4" t="n"/>
+      <c r="J13">
+        <f>IF(H13="","",H13*I13/100)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -948,31 +828,22 @@
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="5">
-        <f>IF(AND(ISNUMBER(H14),ISNUMBER(I14)),H14*I14/100,"")</f>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4">
+        <f>IF(H14="","",H14*I14/100)</f>
         <v/>
       </c>
       <c r="K14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="5">
-        <f>IF(AND(ISNUMBER(H15),ISNUMBER(I15)),H15*I15/100,"")</f>
-        <v/>
-      </c>
-      <c r="K15" s="4" t="n"/>
+      <c r="J15">
+        <f>IF(H15="","",H15*I15/100)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -984,31 +855,22 @@
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="5">
-        <f>IF(AND(ISNUMBER(H16),ISNUMBER(I16)),H16*I16/100,"")</f>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4">
+        <f>IF(H16="","",H16*I16/100)</f>
         <v/>
       </c>
       <c r="K16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="5">
-        <f>IF(AND(ISNUMBER(H17),ISNUMBER(I17)),H17*I17/100,"")</f>
-        <v/>
-      </c>
-      <c r="K17" s="4" t="n"/>
+      <c r="J17">
+        <f>IF(H17="","",H17*I17/100)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1020,31 +882,22 @@
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="5">
-        <f>IF(AND(ISNUMBER(H18),ISNUMBER(I18)),H18*I18/100,"")</f>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4">
+        <f>IF(H18="","",H18*I18/100)</f>
         <v/>
       </c>
       <c r="K18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="5">
-        <f>IF(AND(ISNUMBER(H19),ISNUMBER(I19)),H19*I19/100,"")</f>
-        <v/>
-      </c>
-      <c r="K19" s="4" t="n"/>
+      <c r="J19">
+        <f>IF(H19="","",H19*I19/100)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1056,31 +909,22 @@
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="5">
-        <f>IF(AND(ISNUMBER(H20),ISNUMBER(I20)),H20*I20/100,"")</f>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4">
+        <f>IF(H20="","",H20*I20/100)</f>
         <v/>
       </c>
       <c r="K20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="5">
-        <f>IF(AND(ISNUMBER(H21),ISNUMBER(I21)),H21*I21/100,"")</f>
-        <v/>
-      </c>
-      <c r="K21" s="4" t="n"/>
+      <c r="J21">
+        <f>IF(H21="","",H21*I21/100)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1092,31 +936,22 @@
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="4" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="5">
-        <f>IF(AND(ISNUMBER(H22),ISNUMBER(I22)),H22*I22/100,"")</f>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4">
+        <f>IF(H22="","",H22*I22/100)</f>
         <v/>
       </c>
       <c r="K22" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="5">
-        <f>IF(AND(ISNUMBER(H23),ISNUMBER(I23)),H23*I23/100,"")</f>
-        <v/>
-      </c>
-      <c r="K23" s="4" t="n"/>
+      <c r="J23">
+        <f>IF(H23="","",H23*I23/100)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1128,31 +963,22 @@
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="5">
-        <f>IF(AND(ISNUMBER(H24),ISNUMBER(I24)),H24*I24/100,"")</f>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4">
+        <f>IF(H24="","",H24*I24/100)</f>
         <v/>
       </c>
       <c r="K24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="5">
-        <f>IF(AND(ISNUMBER(H25),ISNUMBER(I25)),H25*I25/100,"")</f>
-        <v/>
-      </c>
-      <c r="K25" s="4" t="n"/>
+      <c r="J25">
+        <f>IF(H25="","",H25*I25/100)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1164,31 +990,22 @@
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="5">
-        <f>IF(AND(ISNUMBER(H26),ISNUMBER(I26)),H26*I26/100,"")</f>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4">
+        <f>IF(H26="","",H26*I26/100)</f>
         <v/>
       </c>
       <c r="K26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="5">
-        <f>IF(AND(ISNUMBER(H27),ISNUMBER(I27)),H27*I27/100,"")</f>
-        <v/>
-      </c>
-      <c r="K27" s="4" t="n"/>
+      <c r="J27">
+        <f>IF(H27="","",H27*I27/100)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -1200,31 +1017,22 @@
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="5">
-        <f>IF(AND(ISNUMBER(H28),ISNUMBER(I28)),H28*I28/100,"")</f>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4">
+        <f>IF(H28="","",H28*I28/100)</f>
         <v/>
       </c>
       <c r="K28" s="4" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="5">
-        <f>IF(AND(ISNUMBER(H29),ISNUMBER(I29)),H29*I29/100,"")</f>
-        <v/>
-      </c>
-      <c r="K29" s="4" t="n"/>
+      <c r="J29">
+        <f>IF(H29="","",H29*I29/100)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -1236,31 +1044,22 @@
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="5">
-        <f>IF(AND(ISNUMBER(H30),ISNUMBER(I30)),H30*I30/100,"")</f>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4">
+        <f>IF(H30="","",H30*I30/100)</f>
         <v/>
       </c>
       <c r="K30" s="4" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="6" t="n"/>
-      <c r="J31" s="5">
-        <f>IF(AND(ISNUMBER(H31),ISNUMBER(I31)),H31*I31/100,"")</f>
-        <v/>
-      </c>
-      <c r="K31" s="4" t="n"/>
+      <c r="J31">
+        <f>IF(H31="","",H31*I31/100)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -1272,31 +1071,22 @@
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="6" t="n"/>
-      <c r="J32" s="5">
-        <f>IF(AND(ISNUMBER(H32),ISNUMBER(I32)),H32*I32/100,"")</f>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4">
+        <f>IF(H32="","",H32*I32/100)</f>
         <v/>
       </c>
       <c r="K32" s="4" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="6" t="n"/>
-      <c r="J33" s="5">
-        <f>IF(AND(ISNUMBER(H33),ISNUMBER(I33)),H33*I33/100,"")</f>
-        <v/>
-      </c>
-      <c r="K33" s="4" t="n"/>
+      <c r="J33">
+        <f>IF(H33="","",H33*I33/100)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -1308,33 +1098,20 @@
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="6" t="n"/>
-      <c r="J34" s="5">
-        <f>IF(AND(ISNUMBER(H34),ISNUMBER(I34)),H34*I34/100,"")</f>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4">
+        <f>IF(H34="","",H34*I34/100)</f>
         <v/>
       </c>
       <c r="K34" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="G5:G34">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>"Vinto"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>"Perso"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
-      <formula>"Negoziazione"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
-      <formula>"Proposta inviata"</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Primo contatto,Qualificato,Proposta inviata,Negoziazione,Vinto,Perso"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1348,23 +1125,23 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AIOsha · Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>AI Osha — Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stato pipeline e forecast pesato</t>
+          <t>Forecast pesato per stadio. Si calcola dal foglio Lead &amp; Clienti.</t>
         </is>
       </c>
     </row>
@@ -1391,143 +1168,139 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Primo contatto</t>
         </is>
       </c>
-      <c r="B5" s="4">
-        <f>COUNTIF('Lead &amp; Clienti'!G5:G34,A5)</f>
-        <v/>
-      </c>
-      <c r="C5" s="5">
-        <f>SUMIF('Lead &amp; Clienti'!G5:G34,A5,'Lead &amp; Clienti'!H5:H34)</f>
-        <v/>
-      </c>
-      <c r="D5" s="5">
-        <f>SUMIF('Lead &amp; Clienti'!G5:G34,A5,'Lead &amp; Clienti'!J5:J34)</f>
+      <c r="B5">
+        <f>COUNTIF('Lead &amp; Clienti'!$G$5:$G$34,A5)</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>SUMIF('Lead &amp; Clienti'!$G$5:$G$34,A5,'Lead &amp; Clienti'!$H$5:$H$34)</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>SUMIF('Lead &amp; Clienti'!$G$5:$G$34,A5,'Lead &amp; Clienti'!$J$5:$J$34)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Qualificato</t>
         </is>
       </c>
-      <c r="B6" s="4">
-        <f>COUNTIF('Lead &amp; Clienti'!G5:G34,A6)</f>
-        <v/>
-      </c>
-      <c r="C6" s="5">
-        <f>SUMIF('Lead &amp; Clienti'!G5:G34,A6,'Lead &amp; Clienti'!H5:H34)</f>
-        <v/>
-      </c>
-      <c r="D6" s="5">
-        <f>SUMIF('Lead &amp; Clienti'!G5:G34,A6,'Lead &amp; Clienti'!J5:J34)</f>
+      <c r="B6">
+        <f>COUNTIF('Lead &amp; Clienti'!$G$5:$G$34,A6)</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>SUMIF('Lead &amp; Clienti'!$G$5:$G$34,A6,'Lead &amp; Clienti'!$H$5:$H$34)</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>SUMIF('Lead &amp; Clienti'!$G$5:$G$34,A6,'Lead &amp; Clienti'!$J$5:$J$34)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Proposta inviata</t>
         </is>
       </c>
-      <c r="B7" s="4">
-        <f>COUNTIF('Lead &amp; Clienti'!G5:G34,A7)</f>
-        <v/>
-      </c>
-      <c r="C7" s="5">
-        <f>SUMIF('Lead &amp; Clienti'!G5:G34,A7,'Lead &amp; Clienti'!H5:H34)</f>
-        <v/>
-      </c>
-      <c r="D7" s="5">
-        <f>SUMIF('Lead &amp; Clienti'!G5:G34,A7,'Lead &amp; Clienti'!J5:J34)</f>
+      <c r="B7">
+        <f>COUNTIF('Lead &amp; Clienti'!$G$5:$G$34,A7)</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>SUMIF('Lead &amp; Clienti'!$G$5:$G$34,A7,'Lead &amp; Clienti'!$H$5:$H$34)</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>SUMIF('Lead &amp; Clienti'!$G$5:$G$34,A7,'Lead &amp; Clienti'!$J$5:$J$34)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Negoziazione</t>
         </is>
       </c>
-      <c r="B8" s="4">
-        <f>COUNTIF('Lead &amp; Clienti'!G5:G34,A8)</f>
-        <v/>
-      </c>
-      <c r="C8" s="5">
-        <f>SUMIF('Lead &amp; Clienti'!G5:G34,A8,'Lead &amp; Clienti'!H5:H34)</f>
-        <v/>
-      </c>
-      <c r="D8" s="5">
-        <f>SUMIF('Lead &amp; Clienti'!G5:G34,A8,'Lead &amp; Clienti'!J5:J34)</f>
+      <c r="B8">
+        <f>COUNTIF('Lead &amp; Clienti'!$G$5:$G$34,A8)</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>SUMIF('Lead &amp; Clienti'!$G$5:$G$34,A8,'Lead &amp; Clienti'!$H$5:$H$34)</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>SUMIF('Lead &amp; Clienti'!$G$5:$G$34,A8,'Lead &amp; Clienti'!$J$5:$J$34)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Vinto</t>
         </is>
       </c>
-      <c r="B9" s="4">
-        <f>COUNTIF('Lead &amp; Clienti'!G5:G34,A9)</f>
-        <v/>
-      </c>
-      <c r="C9" s="5">
-        <f>SUMIF('Lead &amp; Clienti'!G5:G34,A9,'Lead &amp; Clienti'!H5:H34)</f>
-        <v/>
-      </c>
-      <c r="D9" s="5">
-        <f>SUMIF('Lead &amp; Clienti'!G5:G34,A9,'Lead &amp; Clienti'!J5:J34)</f>
+      <c r="B9">
+        <f>COUNTIF('Lead &amp; Clienti'!$G$5:$G$34,A9)</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>SUMIF('Lead &amp; Clienti'!$G$5:$G$34,A9,'Lead &amp; Clienti'!$H$5:$H$34)</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>SUMIF('Lead &amp; Clienti'!$G$5:$G$34,A9,'Lead &amp; Clienti'!$J$5:$J$34)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Perso</t>
         </is>
       </c>
-      <c r="B10" s="4">
-        <f>COUNTIF('Lead &amp; Clienti'!G5:G34,A10)</f>
-        <v/>
-      </c>
-      <c r="C10" s="5">
-        <f>SUMIF('Lead &amp; Clienti'!G5:G34,A10,'Lead &amp; Clienti'!H5:H34)</f>
-        <v/>
-      </c>
-      <c r="D10" s="5">
-        <f>SUMIF('Lead &amp; Clienti'!G5:G34,A10,'Lead &amp; Clienti'!J5:J34)</f>
+      <c r="B10">
+        <f>COUNTIF('Lead &amp; Clienti'!$G$5:$G$34,A10)</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>SUMIF('Lead &amp; Clienti'!$G$5:$G$34,A10,'Lead &amp; Clienti'!$H$5:$H$34)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUMIF('Lead &amp; Clienti'!$G$5:$G$34,A10,'Lead &amp; Clienti'!$J$5:$J$34)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>TOTALE</t>
         </is>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="5">
         <f>SUM(B5:B10)</f>
         <v/>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="5">
         <f>SUM(C5:C10)</f>
         <v/>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="5">
         <f>SUM(D5:D10)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>